--- a/JsonConverter/ExcelFiles/GameSettings.xlsx
+++ b/JsonConverter/ExcelFiles/GameSettings.xlsx
@@ -44,7 +44,7 @@
     <t>float</t>
   </si>
   <si>
-    <t>Name</t>
+    <t>Id</t>
   </si>
   <si>
     <t>DefaultValue</t>

--- a/JsonConverter/ExcelFiles/GameSettings.xlsx
+++ b/JsonConverter/ExcelFiles/GameSettings.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9000"/>
+    <workbookView windowWidth="14136" windowHeight="8111"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -53,10 +53,10 @@
     <t>Desc</t>
   </si>
   <si>
-    <t>CAM_HEIGHT</t>
-  </si>
-  <si>
-    <t>행성들이 한눈에 얼마나 들어올지 결정</t>
+    <t>CAM_HEIGHT_DEFAULT</t>
+  </si>
+  <si>
+    <t>카메라 초기값</t>
   </si>
   <si>
     <t>CAM_SHAKE_PWR</t>
@@ -1298,7 +1298,7 @@
         <v>8</v>
       </c>
       <c r="B4">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>9</v>
@@ -1320,7 +1320,7 @@
         <v>12</v>
       </c>
       <c r="B6">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="C6" t="s">
         <v>13</v>
@@ -1331,7 +1331,7 @@
         <v>14</v>
       </c>
       <c r="B7">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="C7" t="s">
         <v>15</v>
